--- a/export.xlsx
+++ b/export.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Product_ID</t>
   </si>
@@ -22,7 +22,7 @@
     <t>Product_Name</t>
   </si>
   <si>
-    <t>total_sales</t>
+    <t>Total_Sales</t>
   </si>
   <si>
     <t>TEC-CO-10004722</t>
@@ -40,6 +40,21 @@
     <t>OFF-BI-10001359</t>
   </si>
   <si>
+    <t>OFF-BI-10000545</t>
+  </si>
+  <si>
+    <t>TEC-CO-10001449</t>
+  </si>
+  <si>
+    <t>TEC-MA-10001127</t>
+  </si>
+  <si>
+    <t>OFF-BI-10004995</t>
+  </si>
+  <si>
+    <t>OFF-SU-10000151</t>
+  </si>
+  <si>
     <t>Canon imageCLASS 2200 Advanced Copier</t>
   </si>
   <si>
@@ -53,6 +68,21 @@
   </si>
   <si>
     <t>GBC DocuBind TL300 Electric Binding System</t>
+  </si>
+  <si>
+    <t>GBC Ibimaster 500 Manual ProClick Binding System</t>
+  </si>
+  <si>
+    <t>Hewlett Packard LaserJet 3310 Copier</t>
+  </si>
+  <si>
+    <t>HP Designjet T520 Inkjet Large Format Printer - 24" Color</t>
+  </si>
+  <si>
+    <t>GBC DocuBind P400 Electric Binding System</t>
+  </si>
+  <si>
+    <t>High Speed Automatic Electric Letter Opener</t>
   </si>
 </sst>
 </file>
@@ -410,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -429,7 +459,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>61599.824</v>
@@ -440,7 +470,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>27453.384</v>
@@ -451,7 +481,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C4">
         <v>22638.48</v>
@@ -462,7 +492,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C5">
         <v>21870.576</v>
@@ -473,10 +503,65 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>19823.479</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>19024.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>18839.686</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>18374.895</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10">
+        <v>17965.068</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11">
+        <v>17030.312</v>
       </c>
     </row>
   </sheetData>
